--- a/matching_table.xlsx
+++ b/matching_table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://garagekuijpers-my.sharepoint.com/personal/gitte_kuijpersgroup_nl/Documents/Documenten/Exact import facturen/Amortisatie/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_56EDD1BDD3B05C2B57DA2711595ED87656CA7508" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_56EDD1BDD3B05C2B57DA2711595ED87656CA7508" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{814C6A67-3ED3-403F-A240-D54E17CBE116}"/>
   <bookViews>
-    <workbookView xWindow="31245" yWindow="2115" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26391,7 +26391,7 @@
         <v>614</v>
       </c>
       <c r="B895">
-        <v>1483</v>
+        <v>1283</v>
       </c>
       <c r="C895" t="s">
         <v>1781</v>
